--- a/Excel/RelicConfig.xlsx
+++ b/Excel/RelicConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="102">
   <si>
     <t>#</t>
   </si>
@@ -314,6 +314,30 @@
   </si>
   <si>
     <t>极雀战靴</t>
+  </si>
+  <si>
+    <t>极玄神剑</t>
+  </si>
+  <si>
+    <t>极玄神甲</t>
+  </si>
+  <si>
+    <t>极玄面罩</t>
+  </si>
+  <si>
+    <t>极玄项链</t>
+  </si>
+  <si>
+    <t>极玄护腕</t>
+  </si>
+  <si>
+    <t>极玄护戒</t>
+  </si>
+  <si>
+    <t>极玄腰带</t>
+  </si>
+  <si>
+    <t>极玄战靴</t>
   </si>
 </sst>
 </file>
@@ -1287,7 +1311,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N78"/>
+  <dimension ref="A1:N87"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="5" width="9" style="1"/>
@@ -3189,6 +3213,214 @@
         <v>70</v>
       </c>
     </row>
+    <row r="80" customHeight="1" spans="3:10">
+      <c r="C80" s="2">
+        <v>65</v>
+      </c>
+      <c r="D80" s="2">
+        <v>8</v>
+      </c>
+      <c r="E80" s="2">
+        <v>2</v>
+      </c>
+      <c r="F80" s="4">
+        <v>61000065</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I80" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J80" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="3:10">
+      <c r="C81" s="2">
+        <v>66</v>
+      </c>
+      <c r="D81" s="2">
+        <v>8</v>
+      </c>
+      <c r="E81" s="2">
+        <v>2</v>
+      </c>
+      <c r="F81" s="4">
+        <v>61000066</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I81" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J81" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="3:10">
+      <c r="C82" s="2">
+        <v>67</v>
+      </c>
+      <c r="D82" s="2">
+        <v>8</v>
+      </c>
+      <c r="E82" s="2">
+        <v>2</v>
+      </c>
+      <c r="F82" s="4">
+        <v>61000067</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J82" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="3:10">
+      <c r="C83" s="2">
+        <v>68</v>
+      </c>
+      <c r="D83" s="2">
+        <v>8</v>
+      </c>
+      <c r="E83" s="2">
+        <v>2</v>
+      </c>
+      <c r="F83" s="4">
+        <v>61000068</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I83" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J83" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="3:10">
+      <c r="C84" s="2">
+        <v>69</v>
+      </c>
+      <c r="D84" s="2">
+        <v>8</v>
+      </c>
+      <c r="E84" s="2">
+        <v>2</v>
+      </c>
+      <c r="F84" s="4">
+        <v>61000069</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I84" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J84" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="3:10">
+      <c r="C85" s="2">
+        <v>70</v>
+      </c>
+      <c r="D85" s="2">
+        <v>8</v>
+      </c>
+      <c r="E85" s="2">
+        <v>2</v>
+      </c>
+      <c r="F85" s="4">
+        <v>61000070</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I85" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J85" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="3:10">
+      <c r="C86" s="2">
+        <v>71</v>
+      </c>
+      <c r="D86" s="2">
+        <v>8</v>
+      </c>
+      <c r="E86" s="2">
+        <v>2</v>
+      </c>
+      <c r="F86" s="4">
+        <v>61000071</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I86" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J86" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="3:10">
+      <c r="C87" s="2">
+        <v>72</v>
+      </c>
+      <c r="D87" s="2">
+        <v>8</v>
+      </c>
+      <c r="E87" s="2">
+        <v>2</v>
+      </c>
+      <c r="F87" s="4">
+        <v>61000072</v>
+      </c>
+      <c r="G87" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I87" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J87" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:G5" errorStyle="warning">

--- a/Excel/RelicConfig.xlsx
+++ b/Excel/RelicConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="110">
   <si>
     <t>#</t>
   </si>
@@ -338,6 +338,30 @@
   </si>
   <si>
     <t>极玄战靴</t>
+  </si>
+  <si>
+    <t>极麟神剑</t>
+  </si>
+  <si>
+    <t>极麟神甲</t>
+  </si>
+  <si>
+    <t>极麟面罩</t>
+  </si>
+  <si>
+    <t>极麟项链</t>
+  </si>
+  <si>
+    <t>极麟护腕</t>
+  </si>
+  <si>
+    <t>极麟护戒</t>
+  </si>
+  <si>
+    <t>极麟腰带</t>
+  </si>
+  <si>
+    <t>极麟战靴</t>
   </si>
 </sst>
 </file>
@@ -1311,7 +1335,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N87"/>
+  <dimension ref="A1:N96"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="5" width="9" style="1"/>
@@ -3218,7 +3242,7 @@
         <v>65</v>
       </c>
       <c r="D80" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E80" s="2">
         <v>2</v>
@@ -3244,7 +3268,7 @@
         <v>66</v>
       </c>
       <c r="D81" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E81" s="2">
         <v>2</v>
@@ -3270,7 +3294,7 @@
         <v>67</v>
       </c>
       <c r="D82" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E82" s="2">
         <v>2</v>
@@ -3296,7 +3320,7 @@
         <v>68</v>
       </c>
       <c r="D83" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E83" s="2">
         <v>2</v>
@@ -3322,7 +3346,7 @@
         <v>69</v>
       </c>
       <c r="D84" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E84" s="2">
         <v>2</v>
@@ -3348,7 +3372,7 @@
         <v>70</v>
       </c>
       <c r="D85" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E85" s="2">
         <v>2</v>
@@ -3374,7 +3398,7 @@
         <v>71</v>
       </c>
       <c r="D86" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E86" s="2">
         <v>2</v>
@@ -3400,7 +3424,7 @@
         <v>72</v>
       </c>
       <c r="D87" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E87" s="2">
         <v>2</v>
@@ -3418,6 +3442,214 @@
         <v>70</v>
       </c>
       <c r="J87" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="3:10">
+      <c r="C89" s="2">
+        <v>73</v>
+      </c>
+      <c r="D89" s="2">
+        <v>10</v>
+      </c>
+      <c r="E89" s="2">
+        <v>2</v>
+      </c>
+      <c r="F89" s="4">
+        <v>61000073</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I89" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J89" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="3:10">
+      <c r="C90" s="2">
+        <v>74</v>
+      </c>
+      <c r="D90" s="2">
+        <v>10</v>
+      </c>
+      <c r="E90" s="2">
+        <v>2</v>
+      </c>
+      <c r="F90" s="4">
+        <v>61000074</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I90" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J90" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="3:10">
+      <c r="C91" s="2">
+        <v>75</v>
+      </c>
+      <c r="D91" s="2">
+        <v>10</v>
+      </c>
+      <c r="E91" s="2">
+        <v>2</v>
+      </c>
+      <c r="F91" s="4">
+        <v>61000075</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I91" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J91" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="3:10">
+      <c r="C92" s="2">
+        <v>76</v>
+      </c>
+      <c r="D92" s="2">
+        <v>10</v>
+      </c>
+      <c r="E92" s="2">
+        <v>2</v>
+      </c>
+      <c r="F92" s="4">
+        <v>61000076</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I92" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J92" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="3:10">
+      <c r="C93" s="2">
+        <v>77</v>
+      </c>
+      <c r="D93" s="2">
+        <v>10</v>
+      </c>
+      <c r="E93" s="2">
+        <v>2</v>
+      </c>
+      <c r="F93" s="4">
+        <v>61000077</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I93" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J93" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="94" customHeight="1" spans="3:10">
+      <c r="C94" s="2">
+        <v>78</v>
+      </c>
+      <c r="D94" s="2">
+        <v>10</v>
+      </c>
+      <c r="E94" s="2">
+        <v>2</v>
+      </c>
+      <c r="F94" s="4">
+        <v>61000078</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I94" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J94" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="95" customHeight="1" spans="3:10">
+      <c r="C95" s="2">
+        <v>79</v>
+      </c>
+      <c r="D95" s="2">
+        <v>10</v>
+      </c>
+      <c r="E95" s="2">
+        <v>2</v>
+      </c>
+      <c r="F95" s="4">
+        <v>61000079</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I95" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J95" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" spans="3:10">
+      <c r="C96" s="2">
+        <v>80</v>
+      </c>
+      <c r="D96" s="2">
+        <v>10</v>
+      </c>
+      <c r="E96" s="2">
+        <v>2</v>
+      </c>
+      <c r="F96" s="4">
+        <v>61000080</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I96" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J96" s="6" t="s">
         <v>70</v>
       </c>
     </row>
